--- a/data/buy.xlsx
+++ b/data/buy.xlsx
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.382</v>
+        <v>1.386</v>
       </c>
     </row>
     <row r="5">
@@ -1123,15 +1123,15 @@
         <v>1.7008</v>
       </c>
       <c r="E6" t="n">
-        <v>1.382</v>
+        <v>1.386</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-18.74%</t>
+          <t>-18.51%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-6204.38</v>
+        <v>-6126.53</v>
       </c>
     </row>
   </sheetData>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
     </row>
     <row r="5">
@@ -1232,15 +1232,15 @@
         <v>1.7982</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9.859999999999999</v>
+        <v>-10.55</v>
       </c>
     </row>
     <row r="7">
@@ -1256,15 +1256,15 @@
         <v>1.5701</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.98%</t>
+          <t>14.04%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1495.75</v>
+        <v>1402.27</v>
       </c>
     </row>
     <row r="8">
@@ -1280,15 +1280,15 @@
         <v>1.6308</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.70%</t>
+          <t>9.80%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1068.42</v>
+        <v>978.42</v>
       </c>
     </row>
     <row r="9">
@@ -1304,15 +1304,15 @@
         <v>1.9552</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-7.67%</t>
+          <t>-8.42%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-612.42</v>
+        <v>-672.48</v>
       </c>
     </row>
     <row r="10">
@@ -1328,15 +1328,15 @@
         <v>2.1424</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-15.73%</t>
+          <t>-16.42%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-314.22</v>
+        <v>-327.92</v>
       </c>
     </row>
     <row r="11">
@@ -1352,15 +1352,15 @@
         <v>2.1686</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-16.75%</t>
+          <t>-17.43%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-334.55</v>
+        <v>-348.09</v>
       </c>
     </row>
     <row r="12">
@@ -1376,15 +1376,15 @@
         <v>2.3127</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-21.94%</t>
+          <t>-22.58%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-438.13</v>
+        <v>-450.83</v>
       </c>
     </row>
     <row r="13">
@@ -1400,15 +1400,15 @@
         <v>2.3466</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-23.07%</t>
+          <t>-23.69%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-460.66</v>
+        <v>-473.17</v>
       </c>
     </row>
     <row r="14">
@@ -1424,15 +1424,15 @@
         <v>2.4637</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-26.72%</t>
+          <t>-27.32%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-1067.36</v>
+        <v>-1091.19</v>
       </c>
     </row>
     <row r="15">
@@ -1448,15 +1448,15 @@
         <v>2.5933</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-30.39%</t>
+          <t>-30.95%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-606.8099999999999</v>
+        <v>-618.13</v>
       </c>
     </row>
     <row r="16">
@@ -1472,15 +1472,15 @@
         <v>2.6084</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-30.79%</t>
+          <t>-31.35%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-614.85</v>
+        <v>-626.11</v>
       </c>
     </row>
     <row r="17">
@@ -1496,15 +1496,15 @@
         <v>2.6745</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-32.50%</t>
+          <t>-33.05%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-649.01</v>
+        <v>-659.99</v>
       </c>
     </row>
     <row r="18">
@@ -1520,15 +1520,15 @@
         <v>2.5657</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-29.64%</t>
+          <t>-30.21%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-591.86</v>
+        <v>-603.3</v>
       </c>
     </row>
     <row r="19">
@@ -1544,15 +1544,15 @@
         <v>2.5834</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-30.12%</t>
+          <t>-30.69%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-601.48</v>
+        <v>-612.84</v>
       </c>
     </row>
     <row r="20">
@@ -1568,15 +1568,15 @@
         <v>2.4039</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-24.90%</t>
+          <t>-25.51%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-497.27</v>
+        <v>-509.49</v>
       </c>
     </row>
     <row r="21">
@@ -1592,15 +1592,15 @@
         <v>2.4887</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-27.46%</t>
+          <t>-28.05%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-548.38</v>
+        <v>-560.1799999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1616,15 +1616,15 @@
         <v>2.5718</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-29.80%</t>
+          <t>-30.38%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-595.1900000000001</v>
+        <v>-606.6</v>
       </c>
     </row>
     <row r="23">
@@ -1640,15 +1640,15 @@
         <v>2.681</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-32.66%</t>
+          <t>-33.21%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-652.28</v>
+        <v>-663.23</v>
       </c>
     </row>
     <row r="24">
@@ -1664,15 +1664,15 @@
         <v>2.8928</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-37.59%</t>
+          <t>-38.10%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-638.12</v>
+        <v>-646.75</v>
       </c>
     </row>
     <row r="25">
@@ -1688,15 +1688,15 @@
         <v>2.9584</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-38.98%</t>
+          <t>-39.47%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-778.38</v>
+        <v>-788.3</v>
       </c>
     </row>
     <row r="26">
@@ -1712,15 +1712,15 @@
         <v>2.9664</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-39.14%</t>
+          <t>-39.64%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-781.66</v>
+        <v>-791.5599999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1736,15 +1736,15 @@
         <v>3.0088</v>
       </c>
       <c r="E27" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-40.00%</t>
+          <t>-40.49%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-798.79</v>
+        <v>-808.54</v>
       </c>
     </row>
     <row r="28">
@@ -1760,15 +1760,15 @@
         <v>3.049</v>
       </c>
       <c r="E28" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-40.79%</t>
+          <t>-41.27%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-814.59</v>
+        <v>-824.21</v>
       </c>
     </row>
     <row r="29">
@@ -1784,15 +1784,15 @@
         <v>3.1219</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-42.17%</t>
+          <t>-42.64%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-842.1900000000001</v>
+        <v>-851.59</v>
       </c>
     </row>
     <row r="30">
@@ -1808,15 +1808,15 @@
         <v>2.9538</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-38.88%</t>
+          <t>-39.38%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-776.48</v>
+        <v>-786.42</v>
       </c>
     </row>
     <row r="31">
@@ -1832,15 +1832,15 @@
         <v>2.8597</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-36.87%</t>
+          <t>-37.39%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-736.3099999999999</v>
+        <v>-746.5700000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1856,15 +1856,15 @@
         <v>2.8004</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-35.53%</t>
+          <t>-36.06%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-709.62</v>
+        <v>-720.1</v>
       </c>
     </row>
     <row r="33">
@@ -1880,15 +1880,15 @@
         <v>2.7775</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-35.00%</t>
+          <t>-35.53%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-699</v>
+        <v>-709.5700000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1904,15 +1904,15 @@
         <v>2.852</v>
       </c>
       <c r="E34" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-36.70%</t>
+          <t>-37.22%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-732.91</v>
+        <v>-743.2</v>
       </c>
     </row>
     <row r="35">
@@ -1928,15 +1928,15 @@
         <v>2.9647</v>
       </c>
       <c r="E35" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-39.11%</t>
+          <t>-39.60%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-780.96</v>
+        <v>-790.86</v>
       </c>
     </row>
     <row r="36">
@@ -1952,15 +1952,15 @@
         <v>3.1287</v>
       </c>
       <c r="E36" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-42.30%</t>
+          <t>-42.77%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-844.7</v>
+        <v>-854.08</v>
       </c>
     </row>
     <row r="37">
@@ -1976,15 +1976,15 @@
         <v>3.3015</v>
       </c>
       <c r="E37" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-45.32%</t>
+          <t>-45.76%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-905.02</v>
+        <v>-913.91</v>
       </c>
     </row>
     <row r="38">
@@ -2000,15 +2000,15 @@
         <v>3.477</v>
       </c>
       <c r="E38" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-48.08%</t>
+          <t>-48.50%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-960.14</v>
+        <v>-968.58</v>
       </c>
     </row>
     <row r="39">
@@ -2024,15 +2024,15 @@
         <v>3.461</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8053</v>
+        <v>1.7906</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-47.84%</t>
+          <t>-48.26%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-955.34</v>
+        <v>-963.8200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
     </row>
     <row r="5">
@@ -2133,15 +2133,15 @@
         <v>2.5963</v>
       </c>
       <c r="E6" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.48%</t>
+          <t>19.73%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1844.86</v>
+        <v>1969.85</v>
       </c>
     </row>
     <row r="7">
@@ -2157,15 +2157,15 @@
         <v>2.4823</v>
       </c>
       <c r="E7" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.92%</t>
+          <t>25.23%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2388.15</v>
+        <v>2518.88</v>
       </c>
     </row>
     <row r="8">
@@ -2181,15 +2181,15 @@
         <v>2.6702</v>
       </c>
       <c r="E8" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15.20%</t>
+          <t>16.41%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>606.98</v>
+        <v>655.6</v>
       </c>
     </row>
     <row r="9">
@@ -2205,15 +2205,15 @@
         <v>2.847</v>
       </c>
       <c r="E9" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8.04%</t>
+          <t>9.19%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>160.63</v>
+        <v>183.43</v>
       </c>
     </row>
     <row r="10">
@@ -2229,15 +2229,15 @@
         <v>2.9093</v>
       </c>
       <c r="E10" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>114.43</v>
+        <v>136.73</v>
       </c>
     </row>
     <row r="11">
@@ -2253,15 +2253,15 @@
         <v>3.0539</v>
       </c>
       <c r="E11" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>14.45</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="12">
@@ -2277,15 +2277,15 @@
         <v>3.0615</v>
       </c>
       <c r="E12" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9.460000000000001</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="13">
@@ -2301,15 +2301,15 @@
         <v>3.2095</v>
       </c>
       <c r="E13" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.16%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-166.13</v>
+        <v>-125.69</v>
       </c>
     </row>
     <row r="14">
@@ -2325,15 +2325,15 @@
         <v>3.4554</v>
       </c>
       <c r="E14" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-10.98%</t>
+          <t>-10.04%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-219.27</v>
+        <v>-200.49</v>
       </c>
     </row>
     <row r="15">
@@ -2349,15 +2349,15 @@
         <v>3.4435</v>
       </c>
       <c r="E15" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-10.67%</t>
+          <t>-9.73%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-213.12</v>
+        <v>-194.28</v>
       </c>
     </row>
     <row r="16">
@@ -2373,15 +2373,15 @@
         <v>3.4906</v>
       </c>
       <c r="E16" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-11.88%</t>
+          <t>-10.95%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-237.2</v>
+        <v>-218.6</v>
       </c>
     </row>
     <row r="17">
@@ -2397,15 +2397,15 @@
         <v>3.5261</v>
       </c>
       <c r="E17" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.76%</t>
+          <t>-11.84%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-254.91</v>
+        <v>-236.51</v>
       </c>
     </row>
     <row r="18">
@@ -2421,15 +2421,15 @@
         <v>3.3718</v>
       </c>
       <c r="E18" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.77%</t>
+          <t>-7.81%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-175.19</v>
+        <v>-155.94</v>
       </c>
     </row>
     <row r="19">
@@ -2445,15 +2445,15 @@
         <v>3.3854</v>
       </c>
       <c r="E19" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-9.14%</t>
+          <t>-8.18%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-182.51</v>
+        <v>-163.34</v>
       </c>
     </row>
     <row r="20">
@@ -2469,15 +2469,15 @@
         <v>3.3868</v>
       </c>
       <c r="E20" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-9.18%</t>
+          <t>-8.22%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-183.26</v>
+        <v>-164.1</v>
       </c>
     </row>
     <row r="21">
@@ -2493,15 +2493,15 @@
         <v>3.4152</v>
       </c>
       <c r="E21" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-9.93%</t>
+          <t>-8.98%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-198.34</v>
+        <v>-179.34</v>
       </c>
     </row>
     <row r="22">
@@ -2517,15 +2517,15 @@
         <v>3.5143</v>
       </c>
       <c r="E22" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-12.47%</t>
+          <t>-11.55%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-249.06</v>
+        <v>-230.6</v>
       </c>
     </row>
     <row r="23">
@@ -2541,15 +2541,15 @@
         <v>3.5655</v>
       </c>
       <c r="E23" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-13.73%</t>
+          <t>-12.82%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-274.16</v>
+        <v>-255.96</v>
       </c>
     </row>
     <row r="24">
@@ -2565,15 +2565,15 @@
         <v>3.5292</v>
       </c>
       <c r="E24" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-12.84%</t>
+          <t>-11.92%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-256.45</v>
+        <v>-238.06</v>
       </c>
     </row>
     <row r="25">
@@ -2589,15 +2589,15 @@
         <v>3.6271</v>
       </c>
       <c r="E25" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-15.19%</t>
+          <t>-14.30%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-151.71</v>
+        <v>-142.77</v>
       </c>
     </row>
     <row r="26">
@@ -2613,15 +2613,15 @@
         <v>3.4961</v>
       </c>
       <c r="E26" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-12.02%</t>
+          <t>-11.09%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-119.98</v>
+        <v>-110.7</v>
       </c>
     </row>
     <row r="27">
@@ -2637,15 +2637,15 @@
         <v>3.3993</v>
       </c>
       <c r="E27" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-9.51%</t>
+          <t>-8.55%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-284.9</v>
+        <v>-256.26</v>
       </c>
     </row>
     <row r="28">
@@ -2661,15 +2661,15 @@
         <v>3.499</v>
       </c>
       <c r="E28" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-12.09%</t>
+          <t>-11.16%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-301.78</v>
+        <v>-278.59</v>
       </c>
     </row>
     <row r="29">
@@ -2685,15 +2685,15 @@
         <v>3.5435</v>
       </c>
       <c r="E29" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-13.19%</t>
+          <t>-12.28%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-144.91</v>
+        <v>-134.83</v>
       </c>
     </row>
     <row r="30">
@@ -2709,15 +2709,15 @@
         <v>3.7282</v>
       </c>
       <c r="E30" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-17.49%</t>
+          <t>-16.62%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-349.35</v>
+        <v>-331.94</v>
       </c>
     </row>
     <row r="31">
@@ -2733,15 +2733,15 @@
         <v>3.7753</v>
       </c>
       <c r="E31" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-18.52%</t>
+          <t>-17.66%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-369.9</v>
+        <v>-352.71</v>
       </c>
     </row>
     <row r="32">
@@ -2757,15 +2757,15 @@
         <v>3.8269</v>
       </c>
       <c r="E32" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-19.62%</t>
+          <t>-18.77%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-685.73</v>
+        <v>-656.05</v>
       </c>
     </row>
     <row r="33">
@@ -2781,15 +2781,15 @@
         <v>3.9644</v>
       </c>
       <c r="E33" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-22.41%</t>
+          <t>-21.59%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-671.28</v>
+        <v>-646.72</v>
       </c>
     </row>
     <row r="34">
@@ -2805,15 +2805,15 @@
         <v>4.1306</v>
       </c>
       <c r="E34" t="n">
-        <v>3.076</v>
+        <v>3.1085</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-25.53%</t>
+          <t>-24.74%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-2498.33</v>
+        <v>-2421.33</v>
       </c>
     </row>
   </sheetData>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
     </row>
     <row r="5">
@@ -2914,15 +2914,15 @@
         <v>1.502</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.66%</t>
+          <t>32.77%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6322.07</v>
+        <v>6544.11</v>
       </c>
     </row>
     <row r="7">
@@ -2938,15 +2938,15 @@
         <v>1.5997</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.62%</t>
+          <t>24.66%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>943.26</v>
+        <v>984.96</v>
       </c>
     </row>
     <row r="8">
@@ -2962,15 +2962,15 @@
         <v>1.4275</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38.53%</t>
+          <t>39.70%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1538.85</v>
+        <v>1585.58</v>
       </c>
     </row>
     <row r="9">
@@ -2986,15 +2986,15 @@
         <v>1.5591</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>26.84%</t>
+          <t>27.91%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1071.83</v>
+        <v>1114.61</v>
       </c>
     </row>
     <row r="10">
@@ -3010,15 +3010,15 @@
         <v>1.6217</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.94%</t>
+          <t>22.97%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1374.67</v>
+        <v>1439.19</v>
       </c>
     </row>
     <row r="11">
@@ -3034,15 +3034,15 @@
         <v>1.7065</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15.88%</t>
+          <t>16.86%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>317.13</v>
+        <v>336.68</v>
       </c>
     </row>
     <row r="12">
@@ -3058,15 +3058,15 @@
         <v>1.7191</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15.03%</t>
+          <t>16.00%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>300.17</v>
+        <v>319.57</v>
       </c>
     </row>
     <row r="13">
@@ -3082,15 +3082,15 @@
         <v>1.7583</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>12.47%</t>
+          <t>13.42%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>497.92</v>
+        <v>535.85</v>
       </c>
     </row>
     <row r="14">
@@ -3106,15 +3106,15 @@
         <v>1.8989</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>5.02%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>82.66</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="15">
@@ -3130,15 +3130,15 @@
         <v>1.9364</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>42.39</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="16">
@@ -3154,15 +3154,15 @@
         <v>1.9561</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>21.85</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="17">
@@ -3178,15 +3178,15 @@
         <v>1.9321</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>46.92</v>
+        <v>64.19</v>
       </c>
     </row>
     <row r="18">
@@ -3202,15 +3202,15 @@
         <v>1.8952</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>5.22%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>86.72</v>
+        <v>104.32</v>
       </c>
     </row>
     <row r="19">
@@ -3226,15 +3226,15 @@
         <v>1.8675</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5.89%</t>
+          <t>6.78%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>235.25</v>
+        <v>270.97</v>
       </c>
     </row>
     <row r="20">
@@ -3250,15 +3250,15 @@
         <v>1.8935</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9775</v>
+        <v>1.9942</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>5.32%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>88.59</v>
+        <v>106.2</v>
       </c>
     </row>
   </sheetData>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
     </row>
     <row r="5">
@@ -3359,15 +3359,15 @@
         <v>2.644</v>
       </c>
       <c r="E6" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.78%</t>
+          <t>21.75%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1975.1</v>
+        <v>2171.48</v>
       </c>
     </row>
     <row r="7">
@@ -3383,15 +3383,15 @@
         <v>2.569</v>
       </c>
       <c r="E7" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.28%</t>
+          <t>25.30%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2324.26</v>
+        <v>2526.37</v>
       </c>
     </row>
     <row r="8">
@@ -3407,15 +3407,15 @@
         <v>2.941</v>
       </c>
       <c r="E8" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>9.45%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>306.92</v>
+        <v>377.54</v>
       </c>
     </row>
     <row r="9">
@@ -3431,15 +3431,15 @@
         <v>3.149</v>
       </c>
       <c r="E9" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>11.42</v>
+        <v>44.39</v>
       </c>
     </row>
     <row r="10">
@@ -3455,15 +3455,15 @@
         <v>3.21</v>
       </c>
       <c r="E10" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-26.75</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="11">
@@ -3479,15 +3479,15 @@
         <v>3.359</v>
       </c>
       <c r="E11" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.72%</t>
+          <t>-4.17%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-114.15</v>
+        <v>-83.23</v>
       </c>
     </row>
     <row r="12">
@@ -3503,15 +3503,15 @@
         <v>3.382</v>
       </c>
       <c r="E12" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.36%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-126.95</v>
+        <v>-96.25</v>
       </c>
     </row>
     <row r="13">
@@ -3527,15 +3527,15 @@
         <v>3.511</v>
       </c>
       <c r="E13" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9.80%</t>
+          <t>-8.32%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-391.32</v>
+        <v>-332.17</v>
       </c>
     </row>
     <row r="14">
@@ -3551,15 +3551,15 @@
         <v>3.714</v>
       </c>
       <c r="E14" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-14.73%</t>
+          <t>-13.33%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-294.12</v>
+        <v>-266.16</v>
       </c>
     </row>
     <row r="15">
@@ -3575,15 +3575,15 @@
         <v>3.709</v>
       </c>
       <c r="E15" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-14.61%</t>
+          <t>-13.21%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-291.82</v>
+        <v>-263.83</v>
       </c>
     </row>
     <row r="16">
@@ -3599,15 +3599,15 @@
         <v>3.768</v>
       </c>
       <c r="E16" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-15.95%</t>
+          <t>-14.57%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-318.52</v>
+        <v>-290.96</v>
       </c>
     </row>
     <row r="17">
@@ -3623,15 +3623,15 @@
         <v>3.804</v>
       </c>
       <c r="E17" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-16.75%</t>
+          <t>-15.38%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-334.41</v>
+        <v>-307.11</v>
       </c>
     </row>
     <row r="18">
@@ -3647,15 +3647,15 @@
         <v>3.648</v>
       </c>
       <c r="E18" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-13.19%</t>
+          <t>-11.76%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-263.31</v>
+        <v>-234.84</v>
       </c>
     </row>
     <row r="19">
@@ -3671,15 +3671,15 @@
         <v>3.707</v>
       </c>
       <c r="E19" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-14.57%</t>
+          <t>-13.16%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-290.9</v>
+        <v>-262.89</v>
       </c>
     </row>
     <row r="20">
@@ -3695,15 +3695,15 @@
         <v>3.539</v>
       </c>
       <c r="E20" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-10.51%</t>
+          <t>-9.04%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-209.91</v>
+        <v>-180.57</v>
       </c>
     </row>
     <row r="21">
@@ -3719,15 +3719,15 @@
         <v>3.59</v>
       </c>
       <c r="E21" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-11.78%</t>
+          <t>-10.33%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-235.3</v>
+        <v>-206.38</v>
       </c>
     </row>
     <row r="22">
@@ -3743,15 +3743,15 @@
         <v>3.767</v>
       </c>
       <c r="E22" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-15.93%</t>
+          <t>-14.55%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-159.04</v>
+        <v>-145.26</v>
       </c>
     </row>
     <row r="23">
@@ -3767,15 +3767,15 @@
         <v>3.923</v>
       </c>
       <c r="E23" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-19.27%</t>
+          <t>-17.95%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-384.84</v>
+        <v>-358.37</v>
       </c>
     </row>
     <row r="24">
@@ -3791,15 +3791,15 @@
         <v>3.895</v>
       </c>
       <c r="E24" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-18.69%</t>
+          <t>-17.36%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-279.94</v>
+        <v>-259.94</v>
       </c>
     </row>
     <row r="25">
@@ -3815,15 +3815,15 @@
         <v>3.986</v>
       </c>
       <c r="E25" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-20.55%</t>
+          <t>-19.24%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-205.16</v>
+        <v>-192.13</v>
       </c>
     </row>
     <row r="26">
@@ -3839,15 +3839,15 @@
         <v>3.775</v>
       </c>
       <c r="E26" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-16.11%</t>
+          <t>-14.73%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-160.82</v>
+        <v>-147.06</v>
       </c>
     </row>
     <row r="27">
@@ -3863,15 +3863,15 @@
         <v>3.666</v>
       </c>
       <c r="E27" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-13.61%</t>
+          <t>-12.19%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-407.74</v>
+        <v>-365.25</v>
       </c>
     </row>
     <row r="28">
@@ -3887,15 +3887,15 @@
         <v>3.663</v>
       </c>
       <c r="E28" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-13.54%</t>
+          <t>-12.12%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-338.01</v>
+        <v>-302.58</v>
       </c>
     </row>
     <row r="29">
@@ -3911,15 +3911,15 @@
         <v>3.768</v>
       </c>
       <c r="E29" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-15.95%</t>
+          <t>-14.57%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-191.11</v>
+        <v>-174.58</v>
       </c>
     </row>
     <row r="30">
@@ -3935,15 +3935,15 @@
         <v>3.961</v>
       </c>
       <c r="E30" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-20.05%</t>
+          <t>-18.73%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-400.31</v>
+        <v>-374.09</v>
       </c>
     </row>
     <row r="31">
@@ -3959,15 +3959,15 @@
         <v>4.05</v>
       </c>
       <c r="E31" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-21.80%</t>
+          <t>-20.52%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-435.4</v>
+        <v>-409.76</v>
       </c>
     </row>
     <row r="32">
@@ -3983,15 +3983,15 @@
         <v>4.154</v>
       </c>
       <c r="E32" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-23.76%</t>
+          <t>-22.51%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-830.36</v>
+        <v>-786.62</v>
       </c>
     </row>
     <row r="33">
@@ -4007,15 +4007,15 @@
         <v>4.304</v>
       </c>
       <c r="E33" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-26.42%</t>
+          <t>-25.21%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-791.33</v>
+        <v>-755.14</v>
       </c>
     </row>
     <row r="34">
@@ -4031,15 +4031,15 @@
         <v>4.49</v>
       </c>
       <c r="E34" t="n">
-        <v>3.167</v>
+        <v>3.219</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-29.47%</t>
+          <t>-28.31%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-2647.92</v>
+        <v>-2543.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/buy.xlsx
+++ b/data/buy.xlsx
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.386</v>
+        <v>1.389</v>
       </c>
     </row>
     <row r="5">
@@ -1123,15 +1123,15 @@
         <v>1.7008</v>
       </c>
       <c r="E6" t="n">
-        <v>1.386</v>
+        <v>1.389</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-18.51%</t>
+          <t>-18.33%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-6126.53</v>
+        <v>-6068.15</v>
       </c>
     </row>
   </sheetData>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
     </row>
     <row r="5">
@@ -1232,15 +1232,15 @@
         <v>1.7982</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-10.55</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="7">
@@ -1256,15 +1256,15 @@
         <v>1.5701</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.04%</t>
+          <t>16.09%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1402.27</v>
+        <v>1607.04</v>
       </c>
     </row>
     <row r="8">
@@ -1280,15 +1280,15 @@
         <v>1.6308</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.80%</t>
+          <t>11.77%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>978.42</v>
+        <v>1175.57</v>
       </c>
     </row>
     <row r="9">
@@ -1304,15 +1304,15 @@
         <v>1.9552</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.42%</t>
+          <t>-6.77%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-672.48</v>
+        <v>-540.92</v>
       </c>
     </row>
     <row r="10">
@@ -1328,15 +1328,15 @@
         <v>2.1424</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-16.42%</t>
+          <t>-14.92%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-327.92</v>
+        <v>-297.91</v>
       </c>
     </row>
     <row r="11">
@@ -1352,15 +1352,15 @@
         <v>2.1686</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.43%</t>
+          <t>-15.95%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-348.09</v>
+        <v>-318.44</v>
       </c>
     </row>
     <row r="12">
@@ -1376,15 +1376,15 @@
         <v>2.3127</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-22.58%</t>
+          <t>-21.18%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-450.83</v>
+        <v>-423.02</v>
       </c>
     </row>
     <row r="13">
@@ -1400,15 +1400,15 @@
         <v>2.3466</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-23.69%</t>
+          <t>-22.32%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-473.17</v>
+        <v>-445.76</v>
       </c>
     </row>
     <row r="14">
@@ -1424,15 +1424,15 @@
         <v>2.4637</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-27.32%</t>
+          <t>-26.01%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-1091.19</v>
+        <v>-1038.99</v>
       </c>
     </row>
     <row r="15">
@@ -1448,15 +1448,15 @@
         <v>2.5933</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-30.95%</t>
+          <t>-29.71%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-618.13</v>
+        <v>-593.33</v>
       </c>
     </row>
     <row r="16">
@@ -1472,15 +1472,15 @@
         <v>2.6084</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-31.35%</t>
+          <t>-30.12%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-626.11</v>
+        <v>-601.46</v>
       </c>
     </row>
     <row r="17">
@@ -1496,15 +1496,15 @@
         <v>2.6745</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-33.05%</t>
+          <t>-31.85%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-659.99</v>
+        <v>-635.95</v>
       </c>
     </row>
     <row r="18">
@@ -1520,15 +1520,15 @@
         <v>2.5657</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-30.21%</t>
+          <t>-28.96%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-603.3</v>
+        <v>-578.24</v>
       </c>
     </row>
     <row r="19">
@@ -1544,15 +1544,15 @@
         <v>2.5834</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-30.69%</t>
+          <t>-29.44%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-612.84</v>
+        <v>-587.95</v>
       </c>
     </row>
     <row r="20">
@@ -1568,15 +1568,15 @@
         <v>2.4039</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-25.51%</t>
+          <t>-24.17%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-509.49</v>
+        <v>-482.74</v>
       </c>
     </row>
     <row r="21">
@@ -1592,15 +1592,15 @@
         <v>2.4887</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-28.05%</t>
+          <t>-26.76%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-560.1799999999999</v>
+        <v>-534.34</v>
       </c>
     </row>
     <row r="22">
@@ -1616,15 +1616,15 @@
         <v>2.5718</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-30.38%</t>
+          <t>-29.12%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-606.6</v>
+        <v>-581.6</v>
       </c>
     </row>
     <row r="23">
@@ -1640,15 +1640,15 @@
         <v>2.681</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.21%</t>
+          <t>-32.01%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-663.23</v>
+        <v>-639.25</v>
       </c>
     </row>
     <row r="24">
@@ -1664,15 +1664,15 @@
         <v>2.8928</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-38.10%</t>
+          <t>-36.99%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-646.75</v>
+        <v>-627.85</v>
       </c>
     </row>
     <row r="25">
@@ -1688,15 +1688,15 @@
         <v>2.9584</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-39.47%</t>
+          <t>-38.39%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-788.3</v>
+        <v>-766.5599999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1712,15 +1712,15 @@
         <v>2.9664</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-39.64%</t>
+          <t>-38.55%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-791.5599999999999</v>
+        <v>-769.88</v>
       </c>
     </row>
     <row r="27">
@@ -1736,15 +1736,15 @@
         <v>3.0088</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-40.49%</t>
+          <t>-39.42%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-808.54</v>
+        <v>-787.17</v>
       </c>
     </row>
     <row r="28">
@@ -1760,15 +1760,15 @@
         <v>3.049</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-41.27%</t>
+          <t>-40.22%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-824.21</v>
+        <v>-803.12</v>
       </c>
     </row>
     <row r="29">
@@ -1784,15 +1784,15 @@
         <v>3.1219</v>
       </c>
       <c r="E29" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-42.64%</t>
+          <t>-41.61%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-851.59</v>
+        <v>-831</v>
       </c>
     </row>
     <row r="30">
@@ -1808,15 +1808,15 @@
         <v>2.9538</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-39.38%</t>
+          <t>-38.29%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-786.42</v>
+        <v>-764.65</v>
       </c>
     </row>
     <row r="31">
@@ -1832,15 +1832,15 @@
         <v>2.8597</v>
       </c>
       <c r="E31" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-37.39%</t>
+          <t>-36.26%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-746.5700000000001</v>
+        <v>-724.09</v>
       </c>
     </row>
     <row r="32">
@@ -1856,15 +1856,15 @@
         <v>2.8004</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-36.06%</t>
+          <t>-34.91%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-720.1</v>
+        <v>-697.14</v>
       </c>
     </row>
     <row r="33">
@@ -1880,15 +1880,15 @@
         <v>2.7775</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-35.53%</t>
+          <t>-34.37%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-709.5700000000001</v>
+        <v>-686.42</v>
       </c>
     </row>
     <row r="34">
@@ -1904,15 +1904,15 @@
         <v>2.852</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-37.22%</t>
+          <t>-36.09%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-743.2</v>
+        <v>-720.66</v>
       </c>
     </row>
     <row r="35">
@@ -1928,15 +1928,15 @@
         <v>2.9647</v>
       </c>
       <c r="E35" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-39.60%</t>
+          <t>-38.52%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-790.86</v>
+        <v>-769.17</v>
       </c>
     </row>
     <row r="36">
@@ -1952,15 +1952,15 @@
         <v>3.1287</v>
       </c>
       <c r="E36" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-42.77%</t>
+          <t>-41.74%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-854.08</v>
+        <v>-833.53</v>
       </c>
     </row>
     <row r="37">
@@ -1976,15 +1976,15 @@
         <v>3.3015</v>
       </c>
       <c r="E37" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-45.76%</t>
+          <t>-44.79%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-913.91</v>
+        <v>-894.4400000000001</v>
       </c>
     </row>
     <row r="38">
@@ -2000,15 +2000,15 @@
         <v>3.477</v>
       </c>
       <c r="E38" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-48.50%</t>
+          <t>-47.58%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-968.58</v>
+        <v>-950.09</v>
       </c>
     </row>
     <row r="39">
@@ -2024,15 +2024,15 @@
         <v>3.461</v>
       </c>
       <c r="E39" t="n">
-        <v>1.7906</v>
+        <v>1.8228</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-48.26%</t>
+          <t>-47.33%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-963.8200000000001</v>
+        <v>-945.24</v>
       </c>
     </row>
   </sheetData>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
     </row>
     <row r="5">
@@ -2133,15 +2133,15 @@
         <v>2.5963</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.73%</t>
+          <t>20.31%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1969.85</v>
+        <v>2027.54</v>
       </c>
     </row>
     <row r="7">
@@ -2157,15 +2157,15 @@
         <v>2.4823</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.23%</t>
+          <t>25.83%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2518.88</v>
+        <v>2579.22</v>
       </c>
     </row>
     <row r="8">
@@ -2181,15 +2181,15 @@
         <v>2.6702</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.41%</t>
+          <t>16.98%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>655.6</v>
+        <v>678.03</v>
       </c>
     </row>
     <row r="9">
@@ -2205,15 +2205,15 @@
         <v>2.847</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.19%</t>
+          <t>9.71%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>183.43</v>
+        <v>193.95</v>
       </c>
     </row>
     <row r="10">
@@ -2229,15 +2229,15 @@
         <v>2.9093</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>7.36%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>136.73</v>
+        <v>147.03</v>
       </c>
     </row>
     <row r="11">
@@ -2253,15 +2253,15 @@
         <v>3.0539</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>35.7</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="12">
@@ -2277,15 +2277,15 @@
         <v>3.0615</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>30.66</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="13">
@@ -2301,15 +2301,15 @@
         <v>3.2095</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-125.69</v>
+        <v>-107.02</v>
       </c>
     </row>
     <row r="14">
@@ -2325,15 +2325,15 @@
         <v>3.4554</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-10.04%</t>
+          <t>-9.61%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-200.49</v>
+        <v>-191.82</v>
       </c>
     </row>
     <row r="15">
@@ -2349,15 +2349,15 @@
         <v>3.4435</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-9.73%</t>
+          <t>-9.29%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-194.28</v>
+        <v>-185.58</v>
       </c>
     </row>
     <row r="16">
@@ -2373,15 +2373,15 @@
         <v>3.4906</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-10.95%</t>
+          <t>-10.52%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-218.6</v>
+        <v>-210.02</v>
       </c>
     </row>
     <row r="17">
@@ -2397,15 +2397,15 @@
         <v>3.5261</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-11.84%</t>
+          <t>-11.42%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-236.51</v>
+        <v>-228.01</v>
       </c>
     </row>
     <row r="18">
@@ -2421,15 +2421,15 @@
         <v>3.3718</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-7.81%</t>
+          <t>-7.36%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-155.94</v>
+        <v>-147.06</v>
       </c>
     </row>
     <row r="19">
@@ -2445,15 +2445,15 @@
         <v>3.3854</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.18%</t>
+          <t>-7.74%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-163.34</v>
+        <v>-154.49</v>
       </c>
     </row>
     <row r="20">
@@ -2469,15 +2469,15 @@
         <v>3.3868</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-8.22%</t>
+          <t>-7.77%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-164.1</v>
+        <v>-155.25</v>
       </c>
     </row>
     <row r="21">
@@ -2493,15 +2493,15 @@
         <v>3.4152</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.98%</t>
+          <t>-8.54%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-179.34</v>
+        <v>-170.57</v>
       </c>
     </row>
     <row r="22">
@@ -2517,15 +2517,15 @@
         <v>3.5143</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-11.55%</t>
+          <t>-11.12%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-230.6</v>
+        <v>-222.07</v>
       </c>
     </row>
     <row r="23">
@@ -2541,15 +2541,15 @@
         <v>3.5655</v>
       </c>
       <c r="E23" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-12.82%</t>
+          <t>-12.40%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-255.96</v>
+        <v>-247.56</v>
       </c>
     </row>
     <row r="24">
@@ -2565,15 +2565,15 @@
         <v>3.5292</v>
       </c>
       <c r="E24" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-11.92%</t>
+          <t>-11.50%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-238.06</v>
+        <v>-229.57</v>
       </c>
     </row>
     <row r="25">
@@ -2589,15 +2589,15 @@
         <v>3.6271</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-14.30%</t>
+          <t>-13.88%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-142.77</v>
+        <v>-138.64</v>
       </c>
     </row>
     <row r="26">
@@ -2613,15 +2613,15 @@
         <v>3.4961</v>
       </c>
       <c r="E26" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-11.09%</t>
+          <t>-10.66%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-110.7</v>
+        <v>-106.41</v>
       </c>
     </row>
     <row r="27">
@@ -2637,15 +2637,15 @@
         <v>3.3993</v>
       </c>
       <c r="E27" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-8.55%</t>
+          <t>-8.11%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-256.26</v>
+        <v>-243.04</v>
       </c>
     </row>
     <row r="28">
@@ -2661,15 +2661,15 @@
         <v>3.499</v>
       </c>
       <c r="E28" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-11.16%</t>
+          <t>-10.73%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-278.59</v>
+        <v>-267.89</v>
       </c>
     </row>
     <row r="29">
@@ -2685,15 +2685,15 @@
         <v>3.5435</v>
       </c>
       <c r="E29" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-12.28%</t>
+          <t>-11.85%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-134.83</v>
+        <v>-130.18</v>
       </c>
     </row>
     <row r="30">
@@ -2709,15 +2709,15 @@
         <v>3.7282</v>
       </c>
       <c r="E30" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-16.62%</t>
+          <t>-16.22%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-331.94</v>
+        <v>-323.91</v>
       </c>
     </row>
     <row r="31">
@@ -2733,15 +2733,15 @@
         <v>3.7753</v>
       </c>
       <c r="E31" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-17.26%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-352.71</v>
+        <v>-344.78</v>
       </c>
     </row>
     <row r="32">
@@ -2757,15 +2757,15 @@
         <v>3.8269</v>
       </c>
       <c r="E32" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-18.77%</t>
+          <t>-18.38%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-656.05</v>
+        <v>-642.35</v>
       </c>
     </row>
     <row r="33">
@@ -2781,15 +2781,15 @@
         <v>3.9644</v>
       </c>
       <c r="E33" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-21.59%</t>
+          <t>-21.21%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-646.72</v>
+        <v>-635.38</v>
       </c>
     </row>
     <row r="34">
@@ -2805,15 +2805,15 @@
         <v>4.1306</v>
       </c>
       <c r="E34" t="n">
-        <v>3.1085</v>
+        <v>3.1235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-24.74%</t>
+          <t>-24.38%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-2421.33</v>
+        <v>-2385.8</v>
       </c>
     </row>
   </sheetData>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
     </row>
     <row r="5">
@@ -2914,15 +2914,15 @@
         <v>1.502</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32.77%</t>
+          <t>34.71%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6544.11</v>
+        <v>6931.01</v>
       </c>
     </row>
     <row r="7">
@@ -2938,15 +2938,15 @@
         <v>1.5997</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.66%</t>
+          <t>26.48%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>984.96</v>
+        <v>1057.61</v>
       </c>
     </row>
     <row r="8">
@@ -2962,15 +2962,15 @@
         <v>1.4275</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.70%</t>
+          <t>41.74%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1585.58</v>
+        <v>1666.99</v>
       </c>
     </row>
     <row r="9">
@@ -2986,15 +2986,15 @@
         <v>1.5591</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27.91%</t>
+          <t>29.77%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1114.61</v>
+        <v>1189.16</v>
       </c>
     </row>
     <row r="10">
@@ -3010,15 +3010,15 @@
         <v>1.6217</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.97%</t>
+          <t>24.76%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1439.19</v>
+        <v>1551.62</v>
       </c>
     </row>
     <row r="11">
@@ -3034,15 +3034,15 @@
         <v>1.7065</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.86%</t>
+          <t>18.56%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>336.68</v>
+        <v>370.73</v>
       </c>
     </row>
     <row r="12">
@@ -3058,15 +3058,15 @@
         <v>1.7191</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.00%</t>
+          <t>17.70%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>319.57</v>
+        <v>353.37</v>
       </c>
     </row>
     <row r="13">
@@ -3082,15 +3082,15 @@
         <v>1.7583</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13.42%</t>
+          <t>15.07%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>535.85</v>
+        <v>601.95</v>
       </c>
     </row>
     <row r="14">
@@ -3106,15 +3106,15 @@
         <v>1.8989</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>6.55%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>100.22</v>
+        <v>130.83</v>
       </c>
     </row>
     <row r="15">
@@ -3130,15 +3130,15 @@
         <v>1.9364</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>59.61</v>
+        <v>89.62</v>
       </c>
     </row>
     <row r="16">
@@ -3154,15 +3154,15 @@
         <v>1.9561</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>38.9</v>
+        <v>68.61</v>
       </c>
     </row>
     <row r="17">
@@ -3178,15 +3178,15 @@
         <v>1.9321</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>64.19</v>
+        <v>94.26000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -3202,15 +3202,15 @@
         <v>1.8952</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5.22%</t>
+          <t>6.76%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>104.32</v>
+        <v>134.98</v>
       </c>
     </row>
     <row r="19">
@@ -3226,15 +3226,15 @@
         <v>1.8675</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6.78%</t>
+          <t>8.34%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>270.97</v>
+        <v>333.21</v>
       </c>
     </row>
     <row r="20">
@@ -3250,15 +3250,15 @@
         <v>1.8935</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9942</v>
+        <v>2.0233</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>6.86%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>106.2</v>
+        <v>136.89</v>
       </c>
     </row>
   </sheetData>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
     </row>
     <row r="5">
@@ -3359,15 +3359,15 @@
         <v>2.644</v>
       </c>
       <c r="E6" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.75%</t>
+          <t>22.35%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2171.48</v>
+        <v>2231.9</v>
       </c>
     </row>
     <row r="7">
@@ -3383,15 +3383,15 @@
         <v>2.569</v>
       </c>
       <c r="E7" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.30%</t>
+          <t>25.92%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2526.37</v>
+        <v>2588.56</v>
       </c>
     </row>
     <row r="8">
@@ -3407,15 +3407,15 @@
         <v>2.941</v>
       </c>
       <c r="E8" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.45%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>377.54</v>
+        <v>399.26</v>
       </c>
     </row>
     <row r="9">
@@ -3431,15 +3431,15 @@
         <v>3.149</v>
       </c>
       <c r="E9" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>44.39</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="10">
@@ -3455,15 +3455,15 @@
         <v>3.21</v>
       </c>
       <c r="E10" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5.6</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="11">
@@ -3479,15 +3479,15 @@
         <v>3.359</v>
       </c>
       <c r="E11" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-83.23</v>
+        <v>-73.72</v>
       </c>
     </row>
     <row r="12">
@@ -3503,15 +3503,15 @@
         <v>3.382</v>
       </c>
       <c r="E12" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.82%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-96.25</v>
+        <v>-86.8</v>
       </c>
     </row>
     <row r="13">
@@ -3527,15 +3527,15 @@
         <v>3.511</v>
       </c>
       <c r="E13" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-8.32%</t>
+          <t>-7.86%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-332.17</v>
+        <v>-313.97</v>
       </c>
     </row>
     <row r="14">
@@ -3551,15 +3551,15 @@
         <v>3.714</v>
       </c>
       <c r="E14" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-13.33%</t>
+          <t>-12.90%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-266.16</v>
+        <v>-257.56</v>
       </c>
     </row>
     <row r="15">
@@ -3575,15 +3575,15 @@
         <v>3.709</v>
       </c>
       <c r="E15" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-13.21%</t>
+          <t>-12.78%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-263.83</v>
+        <v>-255.21</v>
       </c>
     </row>
     <row r="16">
@@ -3599,15 +3599,15 @@
         <v>3.768</v>
       </c>
       <c r="E16" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-14.57%</t>
+          <t>-14.15%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-290.96</v>
+        <v>-282.48</v>
       </c>
     </row>
     <row r="17">
@@ -3623,15 +3623,15 @@
         <v>3.804</v>
       </c>
       <c r="E17" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-15.38%</t>
+          <t>-14.96%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-307.11</v>
+        <v>-298.71</v>
       </c>
     </row>
     <row r="18">
@@ -3647,15 +3647,15 @@
         <v>3.648</v>
       </c>
       <c r="E18" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-11.76%</t>
+          <t>-11.32%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-234.84</v>
+        <v>-226.08</v>
       </c>
     </row>
     <row r="19">
@@ -3671,15 +3671,15 @@
         <v>3.707</v>
       </c>
       <c r="E19" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-13.16%</t>
+          <t>-12.73%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-262.89</v>
+        <v>-254.27</v>
       </c>
     </row>
     <row r="20">
@@ -3695,15 +3695,15 @@
         <v>3.539</v>
       </c>
       <c r="E20" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-9.04%</t>
+          <t>-8.59%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-180.57</v>
+        <v>-171.54</v>
       </c>
     </row>
     <row r="21">
@@ -3719,15 +3719,15 @@
         <v>3.59</v>
       </c>
       <c r="E21" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-10.33%</t>
+          <t>-9.89%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-206.38</v>
+        <v>-197.48</v>
       </c>
     </row>
     <row r="22">
@@ -3743,15 +3743,15 @@
         <v>3.767</v>
       </c>
       <c r="E22" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-14.55%</t>
+          <t>-14.12%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-145.26</v>
+        <v>-141.02</v>
       </c>
     </row>
     <row r="23">
@@ -3767,15 +3767,15 @@
         <v>3.923</v>
       </c>
       <c r="E23" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-17.95%</t>
+          <t>-17.54%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-358.37</v>
+        <v>-350.23</v>
       </c>
     </row>
     <row r="24">
@@ -3791,15 +3791,15 @@
         <v>3.895</v>
       </c>
       <c r="E24" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-17.36%</t>
+          <t>-16.94%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-259.94</v>
+        <v>-253.79</v>
       </c>
     </row>
     <row r="25">
@@ -3815,15 +3815,15 @@
         <v>3.986</v>
       </c>
       <c r="E25" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-19.24%</t>
+          <t>-18.84%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-192.13</v>
+        <v>-188.13</v>
       </c>
     </row>
     <row r="26">
@@ -3839,15 +3839,15 @@
         <v>3.775</v>
       </c>
       <c r="E26" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-14.73%</t>
+          <t>-14.30%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-147.06</v>
+        <v>-142.83</v>
       </c>
     </row>
     <row r="27">
@@ -3863,15 +3863,15 @@
         <v>3.666</v>
       </c>
       <c r="E27" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-12.19%</t>
+          <t>-11.76%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-365.25</v>
+        <v>-352.17</v>
       </c>
     </row>
     <row r="28">
@@ -3887,15 +3887,15 @@
         <v>3.663</v>
       </c>
       <c r="E28" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-12.12%</t>
+          <t>-11.68%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-302.58</v>
+        <v>-291.67</v>
       </c>
     </row>
     <row r="29">
@@ -3911,15 +3911,15 @@
         <v>3.768</v>
       </c>
       <c r="E29" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-14.57%</t>
+          <t>-14.15%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-174.58</v>
+        <v>-169.49</v>
       </c>
     </row>
     <row r="30">
@@ -3935,15 +3935,15 @@
         <v>3.961</v>
       </c>
       <c r="E30" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-18.73%</t>
+          <t>-18.33%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-374.09</v>
+        <v>-366.03</v>
       </c>
     </row>
     <row r="31">
@@ -3959,15 +3959,15 @@
         <v>4.05</v>
       </c>
       <c r="E31" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-20.52%</t>
+          <t>-20.12%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-409.76</v>
+        <v>-401.87</v>
       </c>
     </row>
     <row r="32">
@@ -3983,15 +3983,15 @@
         <v>4.154</v>
       </c>
       <c r="E32" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-22.51%</t>
+          <t>-22.12%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-786.62</v>
+        <v>-773.15</v>
       </c>
     </row>
     <row r="33">
@@ -4007,15 +4007,15 @@
         <v>4.304</v>
       </c>
       <c r="E33" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-25.21%</t>
+          <t>-24.84%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-755.14</v>
+        <v>-744</v>
       </c>
     </row>
     <row r="34">
@@ -4031,15 +4031,15 @@
         <v>4.49</v>
       </c>
       <c r="E34" t="n">
-        <v>3.219</v>
+        <v>3.235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-28.31%</t>
+          <t>-27.95%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-2543.84</v>
+        <v>-2511.82</v>
       </c>
     </row>
   </sheetData>
